--- a/artfynd/A 59852-2025 artfynd.xlsx
+++ b/artfynd/A 59852-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130093596</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130118365</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130118395</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130118375</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59852-2025 artfynd.xlsx
+++ b/artfynd/A 59852-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130118365</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130118395</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130118375</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
